--- a/data/trans_bre/P15-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P15-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,32</t>
+          <t>-1,29; 2,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,85</t>
+          <t>-2,0; 2,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,17</t>
+          <t>-0,71; 4,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,97</t>
+          <t>1,05; 6,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 53,3</t>
+          <t>-19,12; 54,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 43,35</t>
+          <t>-20,89; 44,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 84,22</t>
+          <t>-10,52; 85,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 110,37</t>
+          <t>11,7; 115,93</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -2,33</t>
+          <t>-5,77; -2,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -1,07</t>
+          <t>-4,76; -1,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,03</t>
+          <t>-2,88; -0,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,94</t>
+          <t>-2,95; 1,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,14; -28,56</t>
+          <t>-61,17; -29,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,46; -12,25</t>
+          <t>-45,81; -11,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,86; -0,51</t>
+          <t>-43,59; -4,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,11; 17,32</t>
+          <t>-44,26; 22,76</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,87</t>
+          <t>-5,64; 0,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,3</t>
+          <t>-2,55; 4,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,07</t>
+          <t>-3,14; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,78</t>
+          <t>-3,14; 1,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 17,22</t>
+          <t>-61,8; 6,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 107,3</t>
+          <t>-38,7; 98,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 77,21</t>
+          <t>-42,08; 72,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 49,43</t>
+          <t>-43,77; 53,69</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -1,03</t>
+          <t>-3,42; -1,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,14</t>
+          <t>-2,41; 0,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,78</t>
+          <t>-1,65; 0,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,53</t>
+          <t>-1,48; 1,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,52; -14,97</t>
+          <t>-42,74; -15,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 2,03</t>
+          <t>-26,82; 5,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 14,66</t>
+          <t>-26,12; 14,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 31,09</t>
+          <t>-22,38; 31,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P15-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,4</t>
+          <t>-1,47; 2,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,9</t>
+          <t>-2,09; 2,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,01</t>
+          <t>-1,14; 4,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,09</t>
+          <t>1,29; 6,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 54,41</t>
+          <t>-22,28; 56,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 44,69</t>
+          <t>-22,17; 40,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 85,72</t>
+          <t>-16,62; 81,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,7; 115,93</t>
+          <t>16,82; 126,43</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-19,76%</t>
+          <t>-18,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -2,25</t>
+          <t>-5,86; -2,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -1,06</t>
+          <t>-4,45; -1,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,23</t>
+          <t>-2,91; -0,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,12</t>
+          <t>-2,7; 0,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,17; -29,94</t>
+          <t>-59,75; -30,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -11,68</t>
+          <t>-43,25; -13,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,59; -4,04</t>
+          <t>-43,89; -2,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 22,76</t>
+          <t>-37,02; 6,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-9,05%</t>
+          <t>-18,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,32</t>
+          <t>-5,41; 0,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,05</t>
+          <t>-2,55; 3,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,91</t>
+          <t>-2,91; 3,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,84</t>
+          <t>-3,88; 1,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,8; 6,87</t>
+          <t>-59,55; 8,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 98,5</t>
+          <t>-38,38; 102,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,08; 72,13</t>
+          <t>-40,96; 75,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 53,69</t>
+          <t>-49,75; 34,12</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>-0,82%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -1,04</t>
+          <t>-3,4; -1,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,42</t>
+          <t>-2,35; 0,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,75</t>
+          <t>-1,64; 0,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,53</t>
+          <t>-1,17; 1,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,74; -15,09</t>
+          <t>-42,0; -15,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 5,4</t>
+          <t>-25,94; 3,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 14,24</t>
+          <t>-25,5; 14,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 31,53</t>
+          <t>-16,66; 19,64</t>
         </is>
       </c>
     </row>
